--- a/InputData/indst/_cement/SYCCU/Start Year Cement Capacity Utilization.xlsx
+++ b/InputData/indst/_cement/SYCCU/Start Year Cement Capacity Utilization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\SYCCU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA58554E-CFE4-454B-8A85-80F0A439751E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{798DC91B-E3CF-482A-B29A-4F533CA0E4F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -512,19 +512,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="110.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.7265625" customWidth="1"/>
+    <col min="2" max="2" width="110.7265625" customWidth="1"/>
+    <col min="3" max="3" width="3.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -532,37 +532,37 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" s="5">
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B8" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="105" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -570,7 +570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
@@ -578,7 +578,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -597,9 +597,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -610,7 +610,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -621,7 +621,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -640,14 +640,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -656,7 +656,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -665,7 +665,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -685,9 +685,9 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -695,7 +695,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>15</v>
       </c>
